--- a/Function_Inventory.xlsx
+++ b/Function_Inventory.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="File Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Function Detail" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="File Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Function Detail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'File Overview'!$A$1:$J$123</definedName>
@@ -6017,7 +6017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K450"/>
+  <dimension ref="A1:K461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6883,7 +6883,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="K16" s="16" t="inlineStr"/>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>CHANGED 2026-08: now requires the rr_group_bonus_v2 stamp before deducting -5. "Group complete" is not proof the bonus was paid (separate best-effort commit).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15339,7 +15343,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="K183" s="16" t="inlineStr"/>
+      <c r="K183" s="16" t="inlineStr">
+        <is>
+          <t>CHANGED 2026-08: skips completed matches with no winner_user_id, which previously marked player 1 as eliminated.</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -16107,7 +16115,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="K199" s="16" t="inlineStr"/>
+      <c r="K199" s="16" t="inlineStr">
+        <is>
+          <t>CHANGED 2026-08: now runTransaction + set(merge). Fixes a lost-update race on the loser deduction (floored at 0, so it needs read-then-write) and a crash when a stats doc is missing.</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -19239,7 +19251,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="K264" s="16" t="inlineStr"/>
+      <c r="K264" s="16" t="inlineStr">
+        <is>
+          <t>CHANGED 2026-08: fetches /programs-tennis.csv (0.15 MB) and prefers the site_stats/court_counts aggregate, falling back to the old full-collection computation.</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -20009,7 +20025,7 @@
       </c>
       <c r="K280" s="16" t="inlineStr">
         <is>
-          <t>The one loose end of the 2026-07 splitMarkerSvg/soloMarkerSvg extraction — courtMarkerHtml was updated, this sibling function was not. One-line, zero-behavior-change fix.</t>
+          <t>The one loose end of the 2026-07 splitMarkerSvg/soloMarkerSvg extraction — courtMarkerHtml was updated, this sibling function was not. One-line, zero-behavior-change fix. | CHANGED 2026-08: now calls soloMarkerSvg — the last inline duplicate SVG from the marker de-dup.</t>
         </is>
       </c>
     </row>
@@ -20593,7 +20609,7 @@
       </c>
       <c r="K292" s="16" t="inlineStr">
         <is>
-          <t>Consolidating into a generic useOAuthSignIn(providerId) is feasible but touches auth-critical, untested code — worth doing given the file admits it is a copy, but not urgent.</t>
+          <t>Consolidating into a generic useOAuthSignIn(providerId) is feasible but touches auth-critical, untested code — worth doing given the file admits it is a copy, but not urgent. | CHANGED 2026-08: now a thin wrapper over useOAuthSignIn; still returns handleGoogleSignIn.</t>
         </is>
       </c>
     </row>
@@ -22379,7 +22395,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="K329" s="16" t="inlineStr"/>
+      <c r="K329" s="16" t="inlineStr">
+        <is>
+          <t>CHANGED 2026-08: sign-out now clears `upcoming` as well as `matches` (was leaking the previous user's opponents/contacts).</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -28456,6 +28476,633 @@
       <c r="K450" s="16" t="inlineStr">
         <is>
           <t>Real but lower-confidence duplication — the two call shapes (single-best vs. top-N list) differ enough that consolidation is only moderate value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Auth &amp; Signup</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>useOAuthSignIn.ts</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>useOAuthSignIn</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>NEW (de-dup). The whole OAuth flow: popup with redirect fallback, getRedirectResult mount effect filtered by providerId, profile bootstrap, analytics, account-exists linking hand-off.</t>
+        </is>
+      </c>
+      <c r="F451" s="16" t="inlineStr">
+        <is>
+          <t>2 (useGoogleSignIn.ts, useAppleSignIn.ts)</t>
+        </is>
+      </c>
+      <c r="G451" s="16" t="inlineStr">
+        <is>
+          <t>No — this IS the de-dup target</t>
+        </is>
+      </c>
+      <c r="H451" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I451" s="16" t="inlineStr">
+        <is>
+          <t>Medium (auth-critical)</t>
+        </is>
+      </c>
+      <c r="J451" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K451" s="16" t="inlineStr">
+        <is>
+          <t>2026-08 audit pass — see CLAUDE.md. Replaced two ~95% identical hooks. Add a provider with a wrapper, never by copying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Auth &amp; Signup</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>useOAuthSignIn.ts</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>completeSignIn</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Internal: shared post-sign-in bookkeeping (bootstrap docs, sessionStorage flags, analytics, navigate) used by both the popup and redirect-return paths.</t>
+        </is>
+      </c>
+      <c r="F452" s="16" t="inlineStr">
+        <is>
+          <t>2 (within useOAuthSignIn)</t>
+        </is>
+      </c>
+      <c r="G452" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H452" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I452" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J452" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K452" s="16" t="inlineStr">
+        <is>
+          <t>2026-08 audit pass — see CLAUDE.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Auth &amp; Signup</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>authMessages.ts</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>getOAuthSignInErrorMessage</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>NEW (de-dup). Provider-parameterised OAuth error copy.</t>
+        </is>
+      </c>
+      <c r="F453" s="16" t="inlineStr">
+        <is>
+          <t>3 (useOAuthSignIn.ts + the two named wrappers)</t>
+        </is>
+      </c>
+      <c r="G453" s="16" t="inlineStr">
+        <is>
+          <t>No — this IS the de-dup target</t>
+        </is>
+      </c>
+      <c r="H453" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I453" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J453" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K453" s="16" t="inlineStr">
+        <is>
+          <t>2026-08 audit pass — see CLAUDE.md. Google/Apple versions were identical apart from providerId and three strings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Cloud Functions</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>courtCounts.js</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>aggregateCourtCounts</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>NEW file. Scheduled every 6h; writes per-court player counts to site_stats/court_counts.</t>
+        </is>
+      </c>
+      <c r="F454" s="16" t="inlineStr">
+        <is>
+          <t>Exported via functions/index.js, onSchedule</t>
+        </is>
+      </c>
+      <c r="G454" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H454" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I454" s="16" t="inlineStr">
+        <is>
+          <t>Low (read-only aggregate; client has a fallback)</t>
+        </is>
+      </c>
+      <c r="J454" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K454" s="16" t="inlineStr">
+        <is>
+          <t>2026-08 audit pass — see CLAUDE.md. Replaces three full-collection reads that ran in the browser on the PUBLIC /courts page. Needs firebase deploy --only functions:aggregateCourtCounts. Keys are raw preferred_courts strings so matchCourtName stays client-side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Cloud Functions</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>courtCounts.js</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>computeCourtCounts</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Internal: applies the active-player filter (has points OR active within 90 days) and tallies per raw court string.</t>
+        </is>
+      </c>
+      <c r="F455" s="16" t="inlineStr">
+        <is>
+          <t>1 (aggregateCourtCounts)</t>
+        </is>
+      </c>
+      <c r="G455" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H455" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I455" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J455" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K455" s="16" t="inlineStr">
+        <is>
+          <t>2026-08 audit pass — see CLAUDE.md. NINETY_DAYS_MS is mirrored from courtMapUtils.ts — keep in step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Admin / One-off Scripts</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>build-programs-csv.mjs</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>(top-level build step)</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>NEW. Filters data/Registered Programs.csv (9.06 MB, 29,299 rows) to 435 tennis rows as public/programs-tennis.csv (0.15 MB). Rows copied verbatim, headers untouched.</t>
+        </is>
+      </c>
+      <c r="F456" s="16" t="inlineStr">
+        <is>
+          <t>Wired into npm run build; also npm run build:programs</t>
+        </is>
+      </c>
+      <c r="G456" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H456" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I456" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J456" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K456" s="16" t="inlineStr">
+        <is>
+          <t>2026-08 audit pass — see CLAUDE.md. Source moved to data/ so the 9 MB original is no longer copied into dist/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Admin / One-off Scripts</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>build-programs-csv.mjs</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>parseCsvLine</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Minimal CSV field splitter matching the app parseCsvLine quoting rules; used only to locate the Section column.</t>
+        </is>
+      </c>
+      <c r="F457" s="16" t="inlineStr">
+        <is>
+          <t>1 (within the script)</t>
+        </is>
+      </c>
+      <c r="G457" s="16" t="inlineStr">
+        <is>
+          <t>Intentional small mirror of the client parser</t>
+        </is>
+      </c>
+      <c r="H457" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I457" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J457" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K457" s="16" t="inlineStr">
+        <is>
+          <t>2026-08 audit pass — see CLAUDE.md. Rows are emitted verbatim, so the two parsers cannot disagree about escaping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Court Map</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>CourtMap.tsx</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>CourtMarker</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>NEW. React.memo wrapper for one court marker; memoizes its SVG html per court.</t>
+        </is>
+      </c>
+      <c r="F458" s="16" t="inlineStr">
+        <is>
+          <t>CourtMap render (~600 instances)</t>
+        </is>
+      </c>
+      <c r="G458" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H458" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I458" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J458" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K458" s="16" t="inlineStr">
+        <is>
+          <t>2026-08 audit pass — see CLAUDE.md. Markers previously rebuilt html + onClick on every render, including every search keystroke.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Court Map</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>CourtMap.tsx</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>PickleballMarker</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>NEW. React.memo wrapper for a pickleball-only marker; html is a module constant.</t>
+        </is>
+      </c>
+      <c r="F459" s="16" t="inlineStr">
+        <is>
+          <t>CourtMap render</t>
+        </is>
+      </c>
+      <c r="G459" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H459" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I459" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J459" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K459" s="16" t="inlineStr">
+        <is>
+          <t>2026-08 audit pass — see CLAUDE.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Court Map</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>CourtMap.tsx</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>handleSelectPickleball</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>NEW useCallback — stable click handler so PickleballMarker memoization holds.</t>
+        </is>
+      </c>
+      <c r="F460" s="16" t="inlineStr">
+        <is>
+          <t>1 (PickleballMarker)</t>
+        </is>
+      </c>
+      <c r="G460" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H460" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I460" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J460" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K460" s="16" t="inlineStr">
+        <is>
+          <t>2026-08 audit pass — see CLAUDE.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Leagues, Friendlies &amp; Matches</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Matches.tsx</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>buildTieredPool</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Hoisted to module scope (pure, closes over nothing).</t>
+        </is>
+      </c>
+      <c r="F461" s="16" t="inlineStr">
+        <is>
+          <t>2 (friendliesExtended, challengesExtended)</t>
+        </is>
+      </c>
+      <c r="G461" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H461" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I461" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J461" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K461" s="16" t="inlineStr">
+        <is>
+          <t>2026-08 audit pass — see CLAUDE.md.</t>
         </is>
       </c>
     </row>
